--- a/example_simple.xlsx
+++ b/example_simple.xlsx
@@ -274,29 +274,30 @@
   <x:cols>
     <x:col min="1" max="1" width="5" hidden="0" customWidth="1"/>
     <x:col min="2" max="2" width="5.559999942779541" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="5.329999923706055" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="4.559999942779541" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="5.670000076293945" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="5.329999923706055" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="4.559999942779541" hidden="0" customWidth="1"/>
     <x:col min="6" max="6" width="9" hidden="0" customWidth="1"/>
     <x:col min="7" max="7" width="7.440000057220459" hidden="0" customWidth="1"/>
     <x:col min="8" max="8" width="11.220000267028809" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1">
+      <x:c r="C1" s="1" t="inlineStr">
+        <x:is>
+          <x:t>REG_DESC</x:t>
+        </x:is>
+      </x:c>
       <x:c r="A1" t="str">
         <x:v>ADDR</x:v>
       </x:c>
       <x:c r="B1" t="str">
         <x:v>REG</x:v>
       </x:c>
-      <x:c r="C1" t="str">
+      <x:c r="D1" t="str">
         <x:v>FIELD</x:v>
       </x:c>
-      <x:c r="D1" t="str">
+      <x:c r="E1" t="str">
         <x:v>BIT</x:v>
-      </x:c>
-      <x:c r="E1" t="str">
-        <x:v>WIDTH</x:v>
       </x:c>
       <x:c r="F1" t="str">
         <x:v>ATTRIBUTE</x:v>
@@ -304,8 +305,10 @@
       <x:c r="G1" t="str">
         <x:v>DEFAULT</x:v>
       </x:c>
-      <x:c r="H1" t="str">
-        <x:v>DESCRIPTION</x:v>
+      <x:c r="H1" s="1" t="inlineStr">
+        <x:is>
+          <x:t>FIELD_DESC</x:t>
+        </x:is>
       </x:c>
     </x:row>
     <x:row r="2">
@@ -315,14 +318,11 @@
       <x:c r="B2" t="str">
         <x:v>status</x:v>
       </x:c>
-      <x:c r="C2" t="str">
+      <x:c r="D2" t="str">
         <x:v>ready</x:v>
       </x:c>
-      <x:c r="D2" t="str">
+      <x:c r="E2" t="str">
         <x:v>[31:0]</x:v>
-      </x:c>
-      <x:c r="E2" t="str">
-        <x:v>32</x:v>
       </x:c>
       <x:c r="F2" t="str">
         <x:v>RO</x:v>
@@ -341,14 +341,11 @@
       <x:c r="B3" t="str">
         <x:v>control</x:v>
       </x:c>
-      <x:c r="C3" t="str">
+      <x:c r="D3" t="str">
         <x:v>enable</x:v>
       </x:c>
-      <x:c r="D3" t="str">
+      <x:c r="E3" t="str">
         <x:v>[31:0]</x:v>
-      </x:c>
-      <x:c r="E3" t="str">
-        <x:v>32</x:v>
       </x:c>
       <x:c r="F3" t="str">
         <x:v>RW</x:v>
